--- a/data/base/Backlog_42.xlsx
+++ b/data/base/Backlog_42.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2BB4F9D-AAFA-4612-B340-92CA3215B80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650EA272-BFD2-4F73-AD52-155AD4F09266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
@@ -236,10 +236,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1991,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B85E2A-DE66-4B81-8117-141128691F08}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="3" bestFit="1" customWidth="1"/>
@@ -2357,6 +2353,9 @@
         <v>25</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E11" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/base/Backlog_42.xlsx
+++ b/data/base/Backlog_42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650EA272-BFD2-4F73-AD52-155AD4F09266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AD4DC6-9115-4B61-8B6F-2FAEC9D9A7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="27">
   <si>
     <t>Status</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Willian Rios</t>
+  </si>
+  <si>
+    <t>SPN</t>
   </si>
 </sst>
 </file>
@@ -2040,7 +2043,7 @@
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>21</v>
@@ -2075,7 +2078,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>22</v>
@@ -2110,7 +2113,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>22</v>
@@ -2145,7 +2148,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>22</v>
@@ -2180,7 +2183,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>23</v>
@@ -2215,7 +2218,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>24</v>
@@ -2250,7 +2253,7 @@
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>22</v>
@@ -2285,7 +2288,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>24</v>
@@ -2320,7 +2323,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>24</v>
